--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -1702,6 +1702,24 @@
       </c>
       <c r="C75" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Λαβράκι φούρνου</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>9</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Γιουβέτσι με χταπόδι</t>
+          <t>Χταπόδι κριθαρότο</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1720,6 +1720,58 @@
         <is>
           <t>Ν</t>
         </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Φιλετίνια κοτόπουλο a la creme με πέννες</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Μακαρόνια με κιμά</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Σπαγγέτι με μπούτι κοτόπουλο κοκκινιστό</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Σνίτσελ κοτόπουλο a la creme</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -1773,6 +1773,11 @@
       <c r="C80" t="n">
         <v>9</v>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
